--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chith\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SLUDI Offline Training\sludi-mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0F3715-F9E2-4CAF-9967-232D03163F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D0F3BB-7C1F-49A7-AE3F-7025C6EF9A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -690,8 +690,8 @@
       <c r="I2">
         <v>-6.6754990000000003</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>38</v>
+      <c r="J2" t="s">
+        <v>48</v>
       </c>
       <c r="K2">
         <v>887311749</v>
@@ -761,8 +761,8 @@
       <c r="I3">
         <v>-6.6754990000000003</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>38</v>
+      <c r="J3" t="s">
+        <v>48</v>
       </c>
       <c r="K3">
         <v>887311749</v>
@@ -832,8 +832,8 @@
       <c r="I4">
         <v>-6.6754990000000003</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>38</v>
+      <c r="J4" t="s">
+        <v>48</v>
       </c>
       <c r="K4">
         <v>887311749</v>
@@ -1118,6 +1118,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SLUDI Offline Training\sludi-mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D0F3BB-7C1F-49A7-AE3F-7025C6EF9A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60715932-65F4-43C9-B313-3B4C9090504C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
   <si>
     <t>lang_code</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>sin</t>
-  </si>
-  <si>
-    <t>01</t>
   </si>
   <si>
     <t>Aluthkade West</t>
@@ -670,19 +667,19 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H2">
         <v>34.256413999999999</v>
@@ -691,7 +688,7 @@
         <v>-6.6754990000000003</v>
       </c>
       <c r="J2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K2">
         <v>887311749</v>
@@ -718,16 +715,16 @@
         <v>27</v>
       </c>
       <c r="S2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T2" t="s">
         <v>29</v>
       </c>
       <c r="U2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>30</v>
@@ -741,19 +738,19 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <v>34.256413999999999</v>
@@ -762,7 +759,7 @@
         <v>-6.6754990000000003</v>
       </c>
       <c r="J3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K3">
         <v>887311749</v>
@@ -795,10 +792,10 @@
         <v>29</v>
       </c>
       <c r="U3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>30</v>
@@ -812,19 +809,19 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H4">
         <v>34.256413999999999</v>
@@ -833,7 +830,7 @@
         <v>-6.6754990000000003</v>
       </c>
       <c r="J4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K4">
         <v>887311749</v>
@@ -845,31 +842,31 @@
         <v>1</v>
       </c>
       <c r="N4" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" t="s">
         <v>42</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>43</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>44</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>45</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>46</v>
-      </c>
-      <c r="S4" t="s">
-        <v>47</v>
       </c>
       <c r="T4" t="s">
         <v>29</v>
       </c>
       <c r="U4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="W4" s="1" t="s">
         <v>30</v>
